--- a/output/pdf_financials_xlsx/ALYA.xlsx
+++ b/output/pdf_financials_xlsx/ALYA.xlsx
@@ -1567,28 +1567,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>14.465</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>12.801</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.903</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>17.655</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>22.583</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>8.859</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>15.956</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>12.833</v>
       </c>
     </row>
     <row r="35">
@@ -1639,28 +1639,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>14.465</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>12.801</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.903</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>17.655</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>22.583</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>8.859</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>15.956</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>12.833</v>
       </c>
     </row>
     <row r="37">
@@ -2071,28 +2071,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>30.675</v>
+        <v>16.21</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>31.92</v>
+        <v>19.119</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>26.328</v>
+        <v>19.425</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>52.858</v>
+        <v>35.203</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>63.627</v>
+        <v>41.044</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>40.807</v>
+        <v>31.948</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>50.435</v>
+        <v>34.479</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>61.754</v>
+        <v>48.921</v>
       </c>
     </row>
     <row r="49">
@@ -4752,22 +4752,22 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-49.867</v>
+        <v>-50.746</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-146.509</v>
+        <v>-146.759</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>-97.518</v>
+        <v>-96.657</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>-159.11</v>
+        <v>-159.136</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-0.604</v>
+        <v>-0.954</v>
       </c>
     </row>
     <row r="125">
@@ -4786,22 +4786,22 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-49.867</v>
+        <v>-50.746</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-146.509</v>
+        <v>-146.759</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-97.518</v>
+        <v>-96.657</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-159.11</v>
+        <v>-159.136</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-0.604</v>
+        <v>-0.954</v>
       </c>
     </row>
     <row r="126">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALYA.xlsx
+++ b/output/pdf_financials_xlsx/ALYA.xlsx
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>5.628</v>
+        <v>0.449</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>6.594</v>
+        <v>0.87</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>9.071999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>15.506</v>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.139</v>
+        <v>-3.04</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.944</v>
+        <v>-6.668</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.254</v>
+        <v>-14.346</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-4.114</v>
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1.846863181888825</v>
+        <v>-2.624807888238443</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-0.5926297947140436</v>
+        <v>-4.186075710967418</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2.985516378808276</v>
+        <v>-6.84845186606708</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-1.430245130248259</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -23816,7 +23816,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -29357,7 +29361,11 @@
           <t>Depreciation of property and equipment 5</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E406" s="5" t="n">
         <v>0.449</v>
       </c>

--- a/output/pdf_financials_xlsx/ALYA.xlsx
+++ b/output/pdf_financials_xlsx/ALYA.xlsx
@@ -980,10 +980,10 @@
         <v>-0.061</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.775</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.215</v>
       </c>
     </row>
     <row r="18">
@@ -1117,15 +1117,11 @@
       <c r="H20" s="3" t="n">
         <v>-16.66</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>-38.777</v>
       </c>
     </row>
     <row r="21">
@@ -1224,10 +1220,10 @@
         <v>-16.66</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.07</v>
+        <v>1.295</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-37.562</v>
+        <v>-38.777</v>
       </c>
     </row>
     <row r="24">
@@ -1508,10 +1504,10 @@
         <v>-0.3674920175914211</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>68.18181818181817</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.234652041957297</v>
       </c>
     </row>
     <row r="32">
@@ -1542,10 +1538,10 @@
         <v>-3.39221175871723</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.8595909867555404</v>
+        <v>0.273506223058581</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>-7.868232967732745</v>
+        <v>-8.122742926089471</v>
       </c>
     </row>
     <row r="33">
@@ -1690,13 +1686,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>98.346</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>95.093</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>72.59399999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1834,13 +1830,13 @@
         <v>92.453</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>98.80800000000001</v>
+        <v>197.154</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>95.27</v>
+        <v>190.363</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>76.489</v>
+        <v>149.083</v>
       </c>
     </row>
     <row r="42">
@@ -2086,13 +2082,13 @@
         <v>41.044</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>31.948</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.479</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>48.921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2669,22 +2665,22 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>15.196</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>53.507</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>53.357</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>41.751</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>42.327</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>37.475</v>
       </c>
     </row>
     <row r="65">
@@ -2777,10 +2773,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>11.13</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>26.903</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -3914,10 +3910,10 @@
         <v>-16.66</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>4.07</v>
+        <v>1.295</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-37.562</v>
+        <v>-38.777</v>
       </c>
     </row>
     <row r="100">
@@ -26080,7 +26076,11 @@
           <t>Income tax (recovery) expense total</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -26861,7 +26861,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
